--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/193.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/193.xlsx
@@ -426,13 +426,13 @@
         <v>-11.89158792178138</v>
       </c>
       <c r="E2">
-        <v>-12.15980614041595</v>
+        <v>-14.87374325558284</v>
       </c>
       <c r="F2">
-        <v>1.283967545883344</v>
+        <v>-0.2240356430921822</v>
       </c>
       <c r="G2">
-        <v>-4.833146036543282</v>
+        <v>-5.972351104244048</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.72103019143878</v>
       </c>
       <c r="E3">
-        <v>-11.67866030557499</v>
+        <v>-16.64161422343727</v>
       </c>
       <c r="F3">
-        <v>1.162174226162389</v>
+        <v>-0.6571665413175476</v>
       </c>
       <c r="G3">
-        <v>-5.785808484197195</v>
+        <v>-5.30851720216385</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.50002644695487</v>
       </c>
       <c r="E4">
-        <v>-13.36687088716049</v>
+        <v>-15.37341507758918</v>
       </c>
       <c r="F4">
-        <v>1.256962192613271</v>
+        <v>-0.5653971183414933</v>
       </c>
       <c r="G4">
-        <v>-5.075706397660143</v>
+        <v>-5.335994730139801</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.23364888506524</v>
       </c>
       <c r="E5">
-        <v>-14.10440986336774</v>
+        <v>-17.7654909026609</v>
       </c>
       <c r="F5">
-        <v>1.151667921119364</v>
+        <v>0.01596231874534254</v>
       </c>
       <c r="G5">
-        <v>-5.487121134007531</v>
+        <v>-4.656101371648599</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.91191734350529</v>
       </c>
       <c r="E6">
-        <v>-14.56226575638726</v>
+        <v>-15.11105340748079</v>
       </c>
       <c r="F6">
-        <v>1.691684715283653</v>
+        <v>-0.3560929608511005</v>
       </c>
       <c r="G6">
-        <v>-5.659875331883319</v>
+        <v>-5.42525696951517</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.53033311303242</v>
       </c>
       <c r="E7">
-        <v>-13.78008508341239</v>
+        <v>-17.82675209903666</v>
       </c>
       <c r="F7">
-        <v>1.564570143686821</v>
+        <v>-0.7551100418049425</v>
       </c>
       <c r="G7">
-        <v>-5.233377750059012</v>
+        <v>-3.706504489164051</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.08487303801964</v>
       </c>
       <c r="E8">
-        <v>-14.8662803304182</v>
+        <v>-16.67494832060773</v>
       </c>
       <c r="F8">
-        <v>1.411376686780448</v>
+        <v>-0.2932895190684338</v>
       </c>
       <c r="G8">
-        <v>-6.730661354923966</v>
+        <v>-7.052241127517691</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.578814447679425</v>
       </c>
       <c r="E9">
-        <v>-16.51067792597949</v>
+        <v>-17.8366332293214</v>
       </c>
       <c r="F9">
-        <v>1.561567437271148</v>
+        <v>-0.00840220491073564</v>
       </c>
       <c r="G9">
-        <v>-5.5444928882031</v>
+        <v>-5.761323689388745</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.016661481542169</v>
       </c>
       <c r="E10">
-        <v>-16.50286177984225</v>
+        <v>-19.05384628631712</v>
       </c>
       <c r="F10">
-        <v>1.756223898749641</v>
+        <v>-0.3460237586407365</v>
       </c>
       <c r="G10">
-        <v>-5.218698791137883</v>
+        <v>-5.109748737440468</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.406341972256685</v>
       </c>
       <c r="E11">
-        <v>-16.2252934940161</v>
+        <v>-20.51839100818978</v>
       </c>
       <c r="F11">
-        <v>1.869108872696249</v>
+        <v>-0.04948195265131947</v>
       </c>
       <c r="G11">
-        <v>-4.183709697013375</v>
+        <v>-5.459564152938637</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.760469194817645</v>
       </c>
       <c r="E12">
-        <v>-17.54992195447377</v>
+        <v>-20.67534791729563</v>
       </c>
       <c r="F12">
-        <v>1.536502123747488</v>
+        <v>0.3354844894207437</v>
       </c>
       <c r="G12">
-        <v>-3.242706990748776</v>
+        <v>-5.585417852159571</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.093033668333438</v>
       </c>
       <c r="E13">
-        <v>-17.63351305618135</v>
+        <v>-22.64487183271162</v>
       </c>
       <c r="F13">
-        <v>1.824622573531555</v>
+        <v>0.2259609312796556</v>
       </c>
       <c r="G13">
-        <v>-2.818828050446032</v>
+        <v>-4.987761755409404</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.432350596683298</v>
       </c>
       <c r="E14">
-        <v>-19.0078415188732</v>
+        <v>-20.93274637989161</v>
       </c>
       <c r="F14">
-        <v>1.483208835987035</v>
+        <v>-0.008162273464546564</v>
       </c>
       <c r="G14">
-        <v>-2.818083177699696</v>
+        <v>-5.363197482835992</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.802798157771741</v>
       </c>
       <c r="E15">
-        <v>-20.22111027500824</v>
+        <v>-22.32898359983257</v>
       </c>
       <c r="F15">
-        <v>1.995279555567479</v>
+        <v>0.378043418486348</v>
       </c>
       <c r="G15">
-        <v>-2.044829124455507</v>
+        <v>-3.149667418913098</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.227911150984699</v>
       </c>
       <c r="E16">
-        <v>-22.57804967025444</v>
+        <v>-23.24184244724677</v>
       </c>
       <c r="F16">
-        <v>2.167098977745336</v>
+        <v>0.2916063333275783</v>
       </c>
       <c r="G16">
-        <v>-2.146370177236033</v>
+        <v>-2.625329974221171</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.727861138562643</v>
       </c>
       <c r="E17">
-        <v>-22.11464186810151</v>
+        <v>-25.11772204865815</v>
       </c>
       <c r="F17">
-        <v>2.452319661998234</v>
+        <v>0.1933896435697701</v>
       </c>
       <c r="G17">
-        <v>-0.8842644169353643</v>
+        <v>-3.266387322991183</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.31547167893033</v>
       </c>
       <c r="E18">
-        <v>-21.97738382092903</v>
+        <v>-25.42972485083862</v>
       </c>
       <c r="F18">
-        <v>2.753665639882137</v>
+        <v>0.6132585884592455</v>
       </c>
       <c r="G18">
-        <v>-0.6074200462138113</v>
+        <v>-2.544860543798106</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.003960550083941</v>
       </c>
       <c r="E19">
-        <v>-23.09560443611708</v>
+        <v>-26.83113811657035</v>
       </c>
       <c r="F19">
-        <v>2.800199670795494</v>
+        <v>0.5268626796542774</v>
       </c>
       <c r="G19">
-        <v>0.02940311481147277</v>
+        <v>-2.504114349300756</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.798310034162738</v>
       </c>
       <c r="E20">
-        <v>-24.48892079032309</v>
+        <v>-26.18980204218205</v>
       </c>
       <c r="F20">
-        <v>3.152358852976271</v>
+        <v>1.76840259723937</v>
       </c>
       <c r="G20">
-        <v>0.5647646761491735</v>
+        <v>-0.7830775925275405</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.699640664695964</v>
       </c>
       <c r="E21">
-        <v>-25.47557112169228</v>
+        <v>-27.04127742442228</v>
       </c>
       <c r="F21">
-        <v>2.9963242276576</v>
+        <v>1.398612017102006</v>
       </c>
       <c r="G21">
-        <v>1.990421317726457</v>
+        <v>-0.7540838346946035</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.703543041564141</v>
       </c>
       <c r="E22">
-        <v>-26.50178673046649</v>
+        <v>-28.67776377589217</v>
       </c>
       <c r="F22">
-        <v>2.845295696737632</v>
+        <v>1.475564287533208</v>
       </c>
       <c r="G22">
-        <v>1.667136614180007</v>
+        <v>-1.251526407425492</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.800978132373559</v>
       </c>
       <c r="E23">
-        <v>-26.05836308410942</v>
+        <v>-28.89874425051847</v>
       </c>
       <c r="F23">
-        <v>3.507957844405383</v>
+        <v>1.609575898391779</v>
       </c>
       <c r="G23">
-        <v>0.9630597205244293</v>
+        <v>-0.5382826131716718</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.981344534504132</v>
       </c>
       <c r="E24">
-        <v>-27.17239033236636</v>
+        <v>-30.57354149209325</v>
       </c>
       <c r="F24">
-        <v>3.572512864930526</v>
+        <v>1.701869528025844</v>
       </c>
       <c r="G24">
-        <v>1.31513623862592</v>
+        <v>-0.417441079897195</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.229342644066143</v>
       </c>
       <c r="E25">
-        <v>-27.63727441704578</v>
+        <v>-30.23528712609032</v>
       </c>
       <c r="F25">
-        <v>3.057821112060029</v>
+        <v>1.719651378044398</v>
       </c>
       <c r="G25">
-        <v>1.081017768634201</v>
+        <v>-1.486459271619872</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.530914517008161</v>
       </c>
       <c r="E26">
-        <v>-27.80078855651475</v>
+        <v>-29.54510466681828</v>
       </c>
       <c r="F26">
-        <v>3.125267979586764</v>
+        <v>1.903874384951976</v>
       </c>
       <c r="G26">
-        <v>1.448355901671732</v>
+        <v>-0.5252787902934146</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.867965969715187</v>
       </c>
       <c r="E27">
-        <v>-28.37200573936828</v>
+        <v>-28.26961241358084</v>
       </c>
       <c r="F27">
-        <v>3.615627674772449</v>
+        <v>2.080443341170235</v>
       </c>
       <c r="G27">
-        <v>1.685467104830952</v>
+        <v>-0.8651162215362198</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.221078789737448</v>
       </c>
       <c r="E28">
-        <v>-28.52113291691487</v>
+        <v>-30.34627775978131</v>
       </c>
       <c r="F28">
-        <v>3.084234159317728</v>
+        <v>2.352446415852876</v>
       </c>
       <c r="G28">
-        <v>1.552396416334408</v>
+        <v>-0.1243286883956633</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.570133942448368</v>
       </c>
       <c r="E29">
-        <v>-27.84695182054894</v>
+        <v>-28.50346281133694</v>
       </c>
       <c r="F29">
-        <v>3.655601995784056</v>
+        <v>0.9688575798883573</v>
       </c>
       <c r="G29">
-        <v>2.033471651919139</v>
+        <v>-0.1810979233030857</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.897690093522587</v>
       </c>
       <c r="E30">
-        <v>-26.76790703400125</v>
+        <v>-30.22439388186487</v>
       </c>
       <c r="F30">
-        <v>3.312618805677335</v>
+        <v>2.204042085634792</v>
       </c>
       <c r="G30">
-        <v>1.214624765508107</v>
+        <v>-0.02805140302257868</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.190763856105664</v>
       </c>
       <c r="E31">
-        <v>-27.95504196663802</v>
+        <v>-29.55870593850032</v>
       </c>
       <c r="F31">
-        <v>3.536985590129472</v>
+        <v>1.884648195138541</v>
       </c>
       <c r="G31">
-        <v>1.408228779190226</v>
+        <v>-0.8054800541917886</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.439719229603682</v>
       </c>
       <c r="E32">
-        <v>-26.53994365245512</v>
+        <v>-27.57249459636606</v>
       </c>
       <c r="F32">
-        <v>2.969535842097942</v>
+        <v>2.301535021789244</v>
       </c>
       <c r="G32">
-        <v>0.5008082468759935</v>
+        <v>-0.4946132069631456</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.637928837262287</v>
       </c>
       <c r="E33">
-        <v>-27.24188429448807</v>
+        <v>-28.77673810380382</v>
       </c>
       <c r="F33">
-        <v>3.455062066829706</v>
+        <v>2.039729429496118</v>
       </c>
       <c r="G33">
-        <v>1.391596598400927</v>
+        <v>-1.577621764134783</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.781226009215761</v>
       </c>
       <c r="E34">
-        <v>-27.131439341915</v>
+        <v>-28.29298386793443</v>
       </c>
       <c r="F34">
-        <v>3.872914954088826</v>
+        <v>1.895620109720706</v>
       </c>
       <c r="G34">
-        <v>0.8845898596070844</v>
+        <v>-1.49914197158082</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.870112215070706</v>
       </c>
       <c r="E35">
-        <v>-26.34305918802363</v>
+        <v>-28.0773560495852</v>
       </c>
       <c r="F35">
-        <v>3.879433487636775</v>
+        <v>1.696312303968567</v>
       </c>
       <c r="G35">
-        <v>0.2407913791305559</v>
+        <v>-2.255485758210412</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.908024646269729</v>
       </c>
       <c r="E36">
-        <v>-25.61823616682993</v>
+        <v>-28.07997803603564</v>
       </c>
       <c r="F36">
-        <v>3.817995200353217</v>
+        <v>2.098180847423158</v>
       </c>
       <c r="G36">
-        <v>0.3643111437463031</v>
+        <v>-1.574241697139187</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.903859640950873</v>
       </c>
       <c r="E37">
-        <v>-23.71120519271978</v>
+        <v>-26.4432245045993</v>
       </c>
       <c r="F37">
-        <v>3.981687043773039</v>
+        <v>2.319085650744144</v>
       </c>
       <c r="G37">
-        <v>0.6781972085067615</v>
+        <v>-1.887492137156105</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.867171997760468</v>
       </c>
       <c r="E38">
-        <v>-23.6218855713925</v>
+        <v>-27.77222294247436</v>
       </c>
       <c r="F38">
-        <v>4.138616462933934</v>
+        <v>1.833828656018005</v>
       </c>
       <c r="G38">
-        <v>0.5088396303542654</v>
+        <v>-1.938851940652358</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.808201265851673</v>
       </c>
       <c r="E39">
-        <v>-23.40213684169628</v>
+        <v>-24.94415016841815</v>
       </c>
       <c r="F39">
-        <v>4.051688428941378</v>
+        <v>2.822624946558117</v>
       </c>
       <c r="G39">
-        <v>-0.2445511496542965</v>
+        <v>-2.134448902749118</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.739339240129395</v>
       </c>
       <c r="E40">
-        <v>-22.47163053107419</v>
+        <v>-25.64209216790233</v>
       </c>
       <c r="F40">
-        <v>4.099034900989356</v>
+        <v>2.332200319429898</v>
       </c>
       <c r="G40">
-        <v>-0.9134071493175686</v>
+        <v>-3.281579416470898</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.671439459125594</v>
       </c>
       <c r="E41">
-        <v>-22.66247401117944</v>
+        <v>-23.04051554981377</v>
       </c>
       <c r="F41">
-        <v>4.085498966530094</v>
+        <v>2.859238643617161</v>
       </c>
       <c r="G41">
-        <v>-0.9548055212861548</v>
+        <v>-3.726228719487029</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.617882903029694</v>
       </c>
       <c r="E42">
-        <v>-22.22455698921569</v>
+        <v>-23.35259986452638</v>
       </c>
       <c r="F42">
-        <v>4.302564866712056</v>
+        <v>2.770367402466361</v>
       </c>
       <c r="G42">
-        <v>-0.4025568671526317</v>
+        <v>-1.854068869391623</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.587425055584958</v>
       </c>
       <c r="E43">
-        <v>-20.48165149856555</v>
+        <v>-23.60237690536745</v>
       </c>
       <c r="F43">
-        <v>4.462905588414808</v>
+        <v>2.731620453539219</v>
       </c>
       <c r="G43">
-        <v>-1.565799806014045</v>
+        <v>-3.586483971183314</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.585449461861807</v>
       </c>
       <c r="E44">
-        <v>-19.85012862735187</v>
+        <v>-22.84525680755103</v>
       </c>
       <c r="F44">
-        <v>4.571981749634784</v>
+        <v>2.684685745029256</v>
       </c>
       <c r="G44">
-        <v>-1.418156096053629</v>
+        <v>-3.061222884285929</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.612522853997861</v>
       </c>
       <c r="E45">
-        <v>-18.76488888836169</v>
+        <v>-20.83404828889444</v>
       </c>
       <c r="F45">
-        <v>4.776609223556884</v>
+        <v>2.613023052355621</v>
       </c>
       <c r="G45">
-        <v>-0.787063489356823</v>
+        <v>-3.201401314055289</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.667590057498147</v>
       </c>
       <c r="E46">
-        <v>-18.15799638727573</v>
+        <v>-20.91279392341382</v>
       </c>
       <c r="F46">
-        <v>4.979957063099309</v>
+        <v>3.355389951335608</v>
       </c>
       <c r="G46">
-        <v>-2.572612847053816</v>
+        <v>-3.601815107575678</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.748846872973538</v>
       </c>
       <c r="E47">
-        <v>-18.05976020062733</v>
+        <v>-21.41926751337969</v>
       </c>
       <c r="F47">
-        <v>4.785615759097988</v>
+        <v>2.754322877837044</v>
       </c>
       <c r="G47">
-        <v>-1.90359463065912</v>
+        <v>-4.047619790985015</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.851927998252703</v>
       </c>
       <c r="E48">
-        <v>-16.13244166296283</v>
+        <v>-18.09919868076013</v>
       </c>
       <c r="F48">
-        <v>5.240578043367687</v>
+        <v>2.850164008721693</v>
       </c>
       <c r="G48">
-        <v>-1.655790365408054</v>
+        <v>-5.482016272785974</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.971742705442395</v>
       </c>
       <c r="E49">
-        <v>-15.61997237341081</v>
+        <v>-19.28045112566095</v>
       </c>
       <c r="F49">
-        <v>4.861099934145578</v>
+        <v>3.259163979913508</v>
       </c>
       <c r="G49">
-        <v>-1.611207248630689</v>
+        <v>-4.781776301410411</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.100818211968503</v>
       </c>
       <c r="E50">
-        <v>-16.19738450870683</v>
+        <v>-17.43646103821159</v>
       </c>
       <c r="F50">
-        <v>5.146524916461568</v>
+        <v>3.06757198938139</v>
       </c>
       <c r="G50">
-        <v>-2.028600830222</v>
+        <v>-3.088124377338047</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.235009774063549</v>
       </c>
       <c r="E51">
-        <v>-14.76862378844278</v>
+        <v>-17.97263236071975</v>
       </c>
       <c r="F51">
-        <v>4.462127988810327</v>
+        <v>3.083819228367883</v>
       </c>
       <c r="G51">
-        <v>-1.99353553187004</v>
+        <v>-4.675097281952937</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.369468377311956</v>
       </c>
       <c r="E52">
-        <v>-14.08024592606281</v>
+        <v>-17.4284999809061</v>
       </c>
       <c r="F52">
-        <v>5.259028217282556</v>
+        <v>3.707998905996371</v>
       </c>
       <c r="G52">
-        <v>-2.451466743589727</v>
+        <v>-3.472538304267139</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.501955769888317</v>
       </c>
       <c r="E53">
-        <v>-14.39321782168092</v>
+        <v>-14.71596216420759</v>
       </c>
       <c r="F53">
-        <v>5.090612179116978</v>
+        <v>3.648771472170766</v>
       </c>
       <c r="G53">
-        <v>-2.220701856229289</v>
+        <v>-2.68474764556001</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.628599501827079</v>
       </c>
       <c r="E54">
-        <v>-12.52958321398629</v>
+        <v>-14.95646941875496</v>
       </c>
       <c r="F54">
-        <v>5.147855229430538</v>
+        <v>3.799833260914958</v>
       </c>
       <c r="G54">
-        <v>-2.791320727560228</v>
+        <v>-3.869055585687806</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.743508326086311</v>
       </c>
       <c r="E55">
-        <v>-11.37551519855352</v>
+        <v>-17.44588026414754</v>
       </c>
       <c r="F55">
-        <v>5.348531357093616</v>
+        <v>3.051207556157154</v>
       </c>
       <c r="G55">
-        <v>-3.23519205237463</v>
+        <v>-4.065658953628504</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.841714388673106</v>
       </c>
       <c r="E56">
-        <v>-10.29836784261504</v>
+        <v>-14.58481755694545</v>
       </c>
       <c r="F56">
-        <v>5.042841273883663</v>
+        <v>3.615451883415835</v>
       </c>
       <c r="G56">
-        <v>-2.256859634609209</v>
+        <v>-3.464162624052783</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.916509788836144</v>
       </c>
       <c r="E57">
-        <v>-10.41553305061549</v>
+        <v>-14.0302968577582</v>
       </c>
       <c r="F57">
-        <v>4.877318666425594</v>
+        <v>3.711465638245267</v>
       </c>
       <c r="G57">
-        <v>-3.013789387799252</v>
+        <v>-4.032623019692116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.965012846993682</v>
       </c>
       <c r="E58">
-        <v>-9.117233138038424</v>
+        <v>-12.9175919239115</v>
       </c>
       <c r="F58">
-        <v>5.007111284725434</v>
+        <v>3.192800367232933</v>
       </c>
       <c r="G58">
-        <v>-3.149912399283004</v>
+        <v>-3.818781641128433</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.982394741605504</v>
       </c>
       <c r="E59">
-        <v>-9.779508876238191</v>
+        <v>-13.60036806394399</v>
       </c>
       <c r="F59">
-        <v>4.643896251548973</v>
+        <v>3.394208167028945</v>
       </c>
       <c r="G59">
-        <v>-3.461954490178089</v>
+        <v>-4.575655115044309</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.963826237046281</v>
       </c>
       <c r="E60">
-        <v>-9.64863144894251</v>
+        <v>-14.53078833355994</v>
       </c>
       <c r="F60">
-        <v>4.373899732261195</v>
+        <v>3.227339409542752</v>
       </c>
       <c r="G60">
-        <v>-2.095129553379194</v>
+        <v>-3.620804396788938</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.904286333351681</v>
       </c>
       <c r="E61">
-        <v>-9.84155802709129</v>
+        <v>-12.15423611738652</v>
       </c>
       <c r="F61">
-        <v>4.819754123811201</v>
+        <v>3.162279186830584</v>
       </c>
       <c r="G61">
-        <v>-3.084906527073875</v>
+        <v>-4.861070488167035</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.802314003719783</v>
       </c>
       <c r="E62">
-        <v>-10.49405226143449</v>
+        <v>-11.18228974112023</v>
       </c>
       <c r="F62">
-        <v>4.954071389911451</v>
+        <v>3.236879653977359</v>
       </c>
       <c r="G62">
-        <v>-2.892044075592554</v>
+        <v>-4.186401170536802</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.658552328535849</v>
       </c>
       <c r="E63">
-        <v>-8.914973374959835</v>
+        <v>-11.20422114073938</v>
       </c>
       <c r="F63">
-        <v>4.698930032110495</v>
+        <v>2.732980856920582</v>
       </c>
       <c r="G63">
-        <v>-2.978101706885908</v>
+        <v>-6.22321762411894</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.474106917076737</v>
       </c>
       <c r="E64">
-        <v>-8.103257994506947</v>
+        <v>-9.531728892434501</v>
       </c>
       <c r="F64">
-        <v>3.928997147966368</v>
+        <v>2.460596109112321</v>
       </c>
       <c r="G64">
-        <v>-2.917303538057193</v>
+        <v>-3.820264765530027</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.251101592309031</v>
       </c>
       <c r="E65">
-        <v>-7.157853004399614</v>
+        <v>-12.33038017086287</v>
       </c>
       <c r="F65">
-        <v>4.111286449951195</v>
+        <v>2.510096421205296</v>
       </c>
       <c r="G65">
-        <v>-2.255909508039438</v>
+        <v>-3.882546058760336</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.990510744472171</v>
       </c>
       <c r="E66">
-        <v>-7.375115601865615</v>
+        <v>-11.53529334696615</v>
       </c>
       <c r="F66">
-        <v>3.43062706826039</v>
+        <v>2.098098494715555</v>
       </c>
       <c r="G66">
-        <v>-2.401331841943004</v>
+        <v>-4.098575707925478</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.69971692722469</v>
       </c>
       <c r="E67">
-        <v>-6.984992094578821</v>
+        <v>-10.16831912606276</v>
       </c>
       <c r="F67">
-        <v>3.648687535757248</v>
+        <v>1.952915422329474</v>
       </c>
       <c r="G67">
-        <v>-2.425555103653851</v>
+        <v>-5.232685846041304</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.384706384299159</v>
       </c>
       <c r="E68">
-        <v>-6.342818252499104</v>
+        <v>-10.50321336435201</v>
       </c>
       <c r="F68">
-        <v>3.230446640548844</v>
+        <v>1.287831788317017</v>
       </c>
       <c r="G68">
-        <v>-2.65336036330218</v>
+        <v>-3.918650868411627</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.051630713663886</v>
       </c>
       <c r="E69">
-        <v>-7.694907379339281</v>
+        <v>-8.868882566509766</v>
       </c>
       <c r="F69">
-        <v>3.711574913953433</v>
+        <v>1.41405314977754</v>
       </c>
       <c r="G69">
-        <v>-2.486568457942619</v>
+        <v>-4.979770098477603</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.706143837077936</v>
       </c>
       <c r="E70">
-        <v>-7.594651493283466</v>
+        <v>-9.310390668361595</v>
       </c>
       <c r="F70">
-        <v>3.059164094676321</v>
+        <v>1.295308463943806</v>
       </c>
       <c r="G70">
-        <v>-2.391635254058478</v>
+        <v>-3.643120784269165</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.351621845291922</v>
       </c>
       <c r="E71">
-        <v>-7.26125617989076</v>
+        <v>-9.91004213950929</v>
       </c>
       <c r="F71">
-        <v>2.757707257378338</v>
+        <v>1.542526541049819</v>
       </c>
       <c r="G71">
-        <v>-3.696364288177264</v>
+        <v>-5.101280361951013</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.994208331741545</v>
       </c>
       <c r="E72">
-        <v>-7.214907248422254</v>
+        <v>-9.478519322844374</v>
       </c>
       <c r="F72">
-        <v>2.815797590356657</v>
+        <v>1.417052688781383</v>
       </c>
       <c r="G72">
-        <v>-2.248752108583534</v>
+        <v>-6.046017363583911</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.63975921770916</v>
       </c>
       <c r="E73">
-        <v>-6.447765637626864</v>
+        <v>-8.770755063237559</v>
       </c>
       <c r="F73">
-        <v>2.4784523933089</v>
+        <v>0.9933955193421762</v>
       </c>
       <c r="G73">
-        <v>-1.799474662903502</v>
+        <v>-4.346264104082669</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.293129530969</v>
       </c>
       <c r="E74">
-        <v>-7.826930510558902</v>
+        <v>-10.52586026286437</v>
       </c>
       <c r="F74">
-        <v>2.447058590947144</v>
+        <v>0.7772972634745481</v>
       </c>
       <c r="G74">
-        <v>-1.380677410003539</v>
+        <v>-4.06467903214888</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.958461934678242</v>
       </c>
       <c r="E75">
-        <v>-7.125660082679086</v>
+        <v>-11.30956703157981</v>
       </c>
       <c r="F75">
-        <v>2.390271647937232</v>
+        <v>0.190143838296077</v>
       </c>
       <c r="G75">
-        <v>-1.202272110892215</v>
+        <v>-3.002745407880243</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.639419076057879</v>
       </c>
       <c r="E76">
-        <v>-6.567276595163293</v>
+        <v>-9.038881480757713</v>
       </c>
       <c r="F76">
-        <v>1.949941222620279</v>
+        <v>0.3956803594136394</v>
       </c>
       <c r="G76">
-        <v>-0.3270234601286203</v>
+        <v>-4.458163853855575</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.340133623647752</v>
       </c>
       <c r="E77">
-        <v>-8.925434149917555</v>
+        <v>-12.43841597526387</v>
       </c>
       <c r="F77">
-        <v>2.142087510222801</v>
+        <v>0.6466827018045951</v>
       </c>
       <c r="G77">
-        <v>-0.1115201877042231</v>
+        <v>-2.276415027109684</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.0674197200515</v>
       </c>
       <c r="E78">
-        <v>-8.674131013335895</v>
+        <v>-12.69535706198507</v>
       </c>
       <c r="F78">
-        <v>2.071428887099554</v>
+        <v>0.03157607536566005</v>
       </c>
       <c r="G78">
-        <v>0.2426386635414692</v>
+        <v>-2.341967139332793</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.827201754700371</v>
       </c>
       <c r="E79">
-        <v>-8.138317440274331</v>
+        <v>-13.11358880743748</v>
       </c>
       <c r="F79">
-        <v>1.919123889211743</v>
+        <v>0.7890230220724618</v>
       </c>
       <c r="G79">
-        <v>-0.05755829541410277</v>
+        <v>-1.997312864330348</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.625209536451042</v>
       </c>
       <c r="E80">
-        <v>-8.854676743547705</v>
+        <v>-12.2250116376524</v>
       </c>
       <c r="F80">
-        <v>2.167037213214634</v>
+        <v>-0.04676193774155222</v>
       </c>
       <c r="G80">
-        <v>0.6052791324587743</v>
+        <v>-1.965707086066926</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.467614620339706</v>
       </c>
       <c r="E81">
-        <v>-10.4272844406654</v>
+        <v>-13.21022191428716</v>
       </c>
       <c r="F81">
-        <v>1.559369253460518</v>
+        <v>-0.0401491736916348</v>
       </c>
       <c r="G81">
-        <v>0.5508007950645276</v>
+        <v>-1.463765481948168</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.359417123409655</v>
       </c>
       <c r="E82">
-        <v>-10.36521717591627</v>
+        <v>-13.49658902511021</v>
       </c>
       <c r="F82">
-        <v>1.815150428451312</v>
+        <v>0.006648544256643149</v>
       </c>
       <c r="G82">
-        <v>1.557140428092183</v>
+        <v>-1.766627430062853</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.308533036873869</v>
       </c>
       <c r="E83">
-        <v>-11.88750446986073</v>
+        <v>-13.30794638337268</v>
       </c>
       <c r="F83">
-        <v>1.305067259794744</v>
+        <v>0.1571275292239531</v>
       </c>
       <c r="G83">
-        <v>2.045906060964642</v>
+        <v>-1.777843558349904</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.321335484371969</v>
       </c>
       <c r="E84">
-        <v>-12.87059089218589</v>
+        <v>-13.97502230402058</v>
       </c>
       <c r="F84">
-        <v>2.021060704164918</v>
+        <v>-0.2054611482629506</v>
       </c>
       <c r="G84">
-        <v>1.434176835127033</v>
+        <v>-0.3639393534370333</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.405093854044957</v>
       </c>
       <c r="E85">
-        <v>-14.0149453308722</v>
+        <v>-16.59360787048195</v>
       </c>
       <c r="F85">
-        <v>1.537487188826891</v>
+        <v>-0.5114735156266956</v>
       </c>
       <c r="G85">
-        <v>2.001452055463308</v>
+        <v>-1.88229127011391</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.565631276512917</v>
       </c>
       <c r="E86">
-        <v>-14.31031957649651</v>
+        <v>-17.27282010147041</v>
       </c>
       <c r="F86">
-        <v>1.094657675575374</v>
+        <v>-0.4073282227744398</v>
       </c>
       <c r="G86">
-        <v>2.490998977083035</v>
+        <v>-1.028809456271023</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.806553725288671</v>
       </c>
       <c r="E87">
-        <v>-14.67720295517594</v>
+        <v>-18.52515147439561</v>
       </c>
       <c r="F87">
-        <v>1.203480443848881</v>
+        <v>-0.02024594959934955</v>
       </c>
       <c r="G87">
-        <v>1.122512146423426</v>
+        <v>1.088569123009278</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.129476717537189</v>
       </c>
       <c r="E88">
-        <v>-16.44012882941399</v>
+        <v>-20.50405385948149</v>
       </c>
       <c r="F88">
-        <v>1.650416506539132</v>
+        <v>-0.8877960908122903</v>
       </c>
       <c r="G88">
-        <v>2.411112202674882</v>
+        <v>0.3688532122261832</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.531088347788399</v>
       </c>
       <c r="E89">
-        <v>-18.5334068825116</v>
+        <v>-21.76903778878413</v>
       </c>
       <c r="F89">
-        <v>0.9261767054672643</v>
+        <v>-0.07244252101336057</v>
       </c>
       <c r="G89">
-        <v>1.973557398749409</v>
+        <v>0.4582544945142016</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.010630658172495</v>
       </c>
       <c r="E90">
-        <v>-20.30658975037703</v>
+        <v>-20.68101756675323</v>
       </c>
       <c r="F90">
-        <v>1.040217784732143</v>
+        <v>-0.8112737965371293</v>
       </c>
       <c r="G90">
-        <v>2.26326654943657</v>
+        <v>0.5663371852803273</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.562302121668735</v>
       </c>
       <c r="E91">
-        <v>-20.52113073496442</v>
+        <v>-26.40504946871464</v>
       </c>
       <c r="F91">
-        <v>0.9069806060662227</v>
+        <v>-1.056180454859559</v>
       </c>
       <c r="G91">
-        <v>2.222298548388089</v>
+        <v>-0.4811988764380188</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.177355791410446</v>
       </c>
       <c r="E92">
-        <v>-21.97664567966578</v>
+        <v>-26.48245467492774</v>
       </c>
       <c r="F92">
-        <v>0.8356552427525763</v>
+        <v>-1.261722518947825</v>
       </c>
       <c r="G92">
-        <v>1.75456812187216</v>
+        <v>1.028635006566313</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.844490803783891</v>
       </c>
       <c r="E93">
-        <v>-23.61818580812823</v>
+        <v>-27.37861251020166</v>
       </c>
       <c r="F93">
-        <v>0.2986379875921295</v>
+        <v>-0.5686856836749034</v>
       </c>
       <c r="G93">
-        <v>1.738942346926799</v>
+        <v>0.7297490236442924</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.544040244341278</v>
       </c>
       <c r="E94">
-        <v>-25.80931059910957</v>
+        <v>-27.65015792559761</v>
       </c>
       <c r="F94">
-        <v>0.3010784784078217</v>
+        <v>-1.116183112730771</v>
       </c>
       <c r="G94">
-        <v>1.101973521897788</v>
+        <v>0.1831746445650801</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.264264175623222</v>
       </c>
       <c r="E95">
-        <v>-27.21255336834039</v>
+        <v>-28.51189482993922</v>
       </c>
       <c r="F95">
-        <v>0.1346420726365438</v>
+        <v>-1.292230237849893</v>
       </c>
       <c r="G95">
-        <v>1.386488426633832</v>
+        <v>-1.798335835237993</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.990408941995556</v>
       </c>
       <c r="E96">
-        <v>-30.08234470919226</v>
+        <v>-32.91240321910083</v>
       </c>
       <c r="F96">
-        <v>0.1935931497799041</v>
+        <v>-0.6535548999773879</v>
       </c>
       <c r="G96">
-        <v>1.605447908601228</v>
+        <v>-0.1746721544113603</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.702279874842841</v>
       </c>
       <c r="E97">
-        <v>-31.75336293920764</v>
+        <v>-33.26344146722742</v>
       </c>
       <c r="F97">
-        <v>0.01524173255381759</v>
+        <v>-1.424571830820633</v>
       </c>
       <c r="G97">
-        <v>1.389964499450067</v>
+        <v>-3.356818184941914</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.387291935049223</v>
       </c>
       <c r="E98">
-        <v>-35.50217636968841</v>
+        <v>-37.85195624752848</v>
       </c>
       <c r="F98">
-        <v>-0.3401181192820628</v>
+        <v>-1.600595200351023</v>
       </c>
       <c r="G98">
-        <v>1.215525233894789</v>
+        <v>-1.208658153237469</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.01819051603944</v>
       </c>
       <c r="E99">
-        <v>-36.28372984901321</v>
+        <v>-38.69198591171433</v>
       </c>
       <c r="F99">
-        <v>-1.073872825493891</v>
+        <v>-2.525557056557517</v>
       </c>
       <c r="G99">
-        <v>0.3190261913146126</v>
+        <v>-2.127854296034889</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.59542935842614</v>
       </c>
       <c r="E100">
-        <v>-38.67126587889223</v>
+        <v>-41.17826078885659</v>
       </c>
       <c r="F100">
-        <v>-0.5606547109777099</v>
+        <v>-2.087608524937385</v>
       </c>
       <c r="G100">
-        <v>1.089933067771458</v>
+        <v>-2.784898269214042</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.08887310057631</v>
       </c>
       <c r="E101">
-        <v>-40.51292153799064</v>
+        <v>-42.55686639524868</v>
       </c>
       <c r="F101">
-        <v>-0.9234318494685509</v>
+        <v>-1.939184398395357</v>
       </c>
       <c r="G101">
-        <v>-0.2124487895599838</v>
+        <v>-2.255495689847029</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.52697692684225</v>
       </c>
       <c r="E102">
-        <v>-43.50023357205257</v>
+        <v>-42.83587020733526</v>
       </c>
       <c r="F102">
-        <v>-0.6935775240194159</v>
+        <v>-2.730776836491991</v>
       </c>
       <c r="G102">
-        <v>-0.06972123972538512</v>
+        <v>-3.511410729989261</v>
       </c>
     </row>
   </sheetData>
